--- a/students/Agametov A. M/Lab3/ЛР3. ОЦЕНКА ПРОЕКТА.xlsx
+++ b/students/Agametov A. M/Lab3/ЛР3. ОЦЕНКА ПРОЕКТА.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUAWEI\Desktop\IT-project-management-AI-23\students\Agametov A. M\Lab3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F2CC8B-31EE-49BE-A0FB-5DFBED71F726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7428693-9E29-4454-B547-05303E550835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10860" yWindow="0" windowWidth="10830" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10710" yWindow="0" windowWidth="10980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="2" r:id="rId1"/>
@@ -236,9 +236,6 @@
     <t>Range finish</t>
   </si>
   <si>
-    <t>Человеко дни</t>
-  </si>
-  <si>
     <t>Человеко месяцы</t>
   </si>
   <si>
@@ -507,6 +504,9 @@
   <si>
     <t>Реализация автосохранения данных</t>
   </si>
+  <si>
+    <t>Человеко часы</t>
+  </si>
 </sst>
 </file>
 
@@ -516,7 +516,7 @@
     <numFmt numFmtId="164" formatCode="0."/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -584,6 +584,14 @@
       <b/>
       <sz val="10"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="7">
@@ -949,9 +957,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1131,6 +1136,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1451,15 +1459,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="71"/>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
+      <c r="A1" s="70"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="62" t="s">
+      <c r="F1" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="62" t="s">
+      <c r="G1" s="61" t="s">
         <v>65</v>
       </c>
       <c r="H1" s="2"/>
@@ -1467,73 +1475,73 @@
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="71"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="61" t="s">
-        <v>66</v>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="60" t="s">
+        <v>126</v>
       </c>
       <c r="F2" s="3">
-        <f>E89/8</f>
-        <v>15</v>
+        <f>E89</f>
+        <v>293</v>
       </c>
       <c r="G2" s="3">
-        <f>E89/8</f>
-        <v>15</v>
+        <f>G89</f>
+        <v>751</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="73" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="73"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="72" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="72"/>
       <c r="F3" s="3">
         <f>F2/22</f>
-        <v>0.68181818181818177</v>
+        <v>13.318181818181818</v>
       </c>
       <c r="G3" s="3">
         <f>G2/22</f>
-        <v>0.68181818181818177</v>
+        <v>34.136363636363633</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="71"/>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="73" t="s">
+      <c r="A4" s="70"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="73"/>
+      <c r="E4" s="72"/>
       <c r="F4" s="3">
         <f>F3/4</f>
-        <v>0.17045454545454544</v>
+        <v>3.3295454545454546</v>
       </c>
       <c r="G4" s="3">
         <f>G3/4</f>
-        <v>0.17045454545454544</v>
+        <v>8.5340909090909083</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="71"/>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="73" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="73"/>
+      <c r="A5" s="70"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="72"/>
       <c r="F5" s="4">
         <v>300</v>
       </c>
@@ -1545,20 +1553,20 @@
       <c r="J5" s="2"/>
     </row>
     <row r="6" spans="1:10" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="72"/>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="74" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="74"/>
+      <c r="A6" s="71"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="73" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="73"/>
       <c r="F6" s="5">
         <f>F5*H89</f>
-        <v>214800</v>
+        <v>146999.99999999997</v>
       </c>
       <c r="G6" s="5">
         <f>G5*H89</f>
-        <v>250600</v>
+        <v>171499.99999999997</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -1566,27 +1574,29 @@
     </row>
     <row r="7" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="H7" s="14"/>
+      <c r="H7" s="63" t="s">
+        <v>122</v>
+      </c>
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -1596,1472 +1606,1710 @@
         <v>44</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="70"/>
+        <v>70</v>
+      </c>
+      <c r="E8" s="67"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="69"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="21" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="65">
-        <v>1</v>
-      </c>
-      <c r="F10" s="66">
-        <v>2</v>
-      </c>
-      <c r="G10" s="67">
+      <c r="E10" s="64">
         <v>4</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="F10" s="65">
+        <v>6</v>
+      </c>
+      <c r="G10" s="66">
+        <v>10</v>
+      </c>
+      <c r="H10" s="74">
+        <f>(E10 + 4*F10 + G10)/6</f>
+        <v>6.333333333333333</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="21" t="s">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="65">
-        <v>2</v>
-      </c>
-      <c r="F11" s="66">
-        <v>4</v>
-      </c>
-      <c r="G11" s="67">
+      <c r="E11" s="64">
         <v>6</v>
       </c>
-      <c r="H11" s="2"/>
+      <c r="F11" s="65">
+        <v>10</v>
+      </c>
+      <c r="G11" s="66">
+        <v>16</v>
+      </c>
+      <c r="H11" s="74">
+        <f>(E11 + 4*F11 + G11)/6</f>
+        <v>10.333333333333334</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="20" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12" s="64">
+        <v>8</v>
+      </c>
+      <c r="F12" s="65">
+        <v>12</v>
+      </c>
+      <c r="G12" s="66">
+        <v>20</v>
+      </c>
+      <c r="H12" s="74">
+        <f t="shared" ref="H12:H75" si="0">(E12 + 4*F12 + G12)/6</f>
+        <v>12.666666666666666</v>
+      </c>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D13" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="64">
+        <v>2</v>
+      </c>
+      <c r="F13" s="65">
+        <v>4</v>
+      </c>
+      <c r="G13" s="66">
+        <v>6</v>
+      </c>
+      <c r="H13" s="74">
+        <f>(E13 + 4*F13 + G13)/6</f>
+        <v>4</v>
+      </c>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="64">
+        <v>3</v>
+      </c>
+      <c r="F14" s="65">
+        <v>5</v>
+      </c>
+      <c r="G14" s="66">
+        <v>8</v>
+      </c>
+      <c r="H14" s="74">
+        <f>(E14 + 4*F14 + G14)/6</f>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="25"/>
+      <c r="C15" s="15">
+        <v>1.2</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="74"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="64">
+        <v>8</v>
+      </c>
+      <c r="F16" s="65">
+        <v>12</v>
+      </c>
+      <c r="G16" s="66">
+        <v>18</v>
+      </c>
+      <c r="H16" s="74">
+        <f>(E16 + 4*F16 + G16)/6</f>
+        <v>12.333333333333334</v>
+      </c>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="64">
+        <v>3</v>
+      </c>
+      <c r="F17" s="65">
+        <v>5</v>
+      </c>
+      <c r="G17" s="66">
+        <v>8</v>
+      </c>
+      <c r="H17" s="74">
+        <f>(E17 + 4*F17 + G17)/6</f>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="64">
+        <v>6</v>
+      </c>
+      <c r="F18" s="65">
+        <v>10</v>
+      </c>
+      <c r="G18" s="66">
+        <v>15</v>
+      </c>
+      <c r="H18" s="74">
+        <f t="shared" si="0"/>
+        <v>10.166666666666666</v>
+      </c>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="64">
+        <v>6</v>
+      </c>
+      <c r="F19" s="65">
+        <v>10</v>
+      </c>
+      <c r="G19" s="66">
+        <v>15</v>
+      </c>
+      <c r="H19" s="74">
+        <f t="shared" si="0"/>
+        <v>10.166666666666666</v>
+      </c>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="74"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="64">
+        <v>6</v>
+      </c>
+      <c r="F21" s="65">
+        <v>10</v>
+      </c>
+      <c r="G21" s="66">
+        <v>16</v>
+      </c>
+      <c r="H21" s="74">
+        <f t="shared" si="0"/>
+        <v>10.333333333333334</v>
+      </c>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="64">
+        <v>3</v>
+      </c>
+      <c r="F22" s="65">
+        <v>5</v>
+      </c>
+      <c r="G22" s="66">
+        <v>8</v>
+      </c>
+      <c r="H22" s="74">
+        <f t="shared" si="0"/>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="64">
+        <v>2</v>
+      </c>
+      <c r="F23" s="65">
+        <v>4</v>
+      </c>
+      <c r="G23" s="66">
+        <v>6</v>
+      </c>
+      <c r="H23" s="74">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="15">
+        <v>1.4</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="74"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="64">
+        <v>6</v>
+      </c>
+      <c r="F25" s="65">
+        <v>10</v>
+      </c>
+      <c r="G25" s="66">
+        <v>15</v>
+      </c>
+      <c r="H25" s="74">
+        <f t="shared" si="0"/>
+        <v>10.166666666666666</v>
+      </c>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="64">
+        <v>8</v>
+      </c>
+      <c r="F26" s="65">
+        <v>12</v>
+      </c>
+      <c r="G26" s="66">
+        <v>18</v>
+      </c>
+      <c r="H26" s="74">
+        <f t="shared" si="0"/>
+        <v>12.333333333333334</v>
+      </c>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="64">
+        <v>6</v>
+      </c>
+      <c r="F27" s="65">
+        <v>10</v>
+      </c>
+      <c r="G27" s="66">
+        <v>15</v>
+      </c>
+      <c r="H27" s="74">
+        <f t="shared" si="0"/>
+        <v>10.166666666666666</v>
+      </c>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="74"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="21">
+        <v>12</v>
+      </c>
+      <c r="F29" s="22">
+        <v>20</v>
+      </c>
+      <c r="G29" s="23">
+        <v>30</v>
+      </c>
+      <c r="H29" s="74">
+        <f t="shared" si="0"/>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="28"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="15">
+        <v>1.6</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="74"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="18"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="31">
+        <v>4</v>
+      </c>
+      <c r="F31" s="32">
+        <v>6</v>
+      </c>
+      <c r="G31" s="23">
+        <v>10</v>
+      </c>
+      <c r="H31" s="74">
+        <f t="shared" si="0"/>
+        <v>6.333333333333333</v>
+      </c>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="21">
+        <v>5</v>
+      </c>
+      <c r="F32" s="22">
+        <v>8</v>
+      </c>
+      <c r="G32" s="23">
+        <v>12</v>
+      </c>
+      <c r="H32" s="74">
+        <f t="shared" si="0"/>
+        <v>8.1666666666666661</v>
+      </c>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="15">
+        <v>1.7</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="74"/>
+      <c r="J33" s="2"/>
+    </row>
+    <row r="34" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="E12" s="65">
+      <c r="E34" s="21">
+        <v>4</v>
+      </c>
+      <c r="F34" s="22">
+        <v>7</v>
+      </c>
+      <c r="G34" s="23">
+        <v>12</v>
+      </c>
+      <c r="H34" s="74">
+        <f t="shared" si="0"/>
+        <v>7.333333333333333</v>
+      </c>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="21">
+        <v>4</v>
+      </c>
+      <c r="F35" s="22">
+        <v>6</v>
+      </c>
+      <c r="G35" s="23">
+        <v>10</v>
+      </c>
+      <c r="H35" s="74">
+        <f t="shared" si="0"/>
+        <v>6.333333333333333</v>
+      </c>
+      <c r="J35" s="2"/>
+    </row>
+    <row r="36" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="25"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="15">
+        <v>1.8</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="74"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="21">
+        <v>4</v>
+      </c>
+      <c r="F37" s="22">
+        <v>6</v>
+      </c>
+      <c r="G37" s="23">
+        <v>9</v>
+      </c>
+      <c r="H37" s="74">
+        <f t="shared" si="0"/>
+        <v>6.166666666666667</v>
+      </c>
+      <c r="J37" s="2"/>
+    </row>
+    <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="24"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="21">
         <v>2</v>
       </c>
-      <c r="F12" s="66">
+      <c r="F38" s="22">
+        <v>3</v>
+      </c>
+      <c r="G38" s="23">
+        <v>5</v>
+      </c>
+      <c r="H38" s="74">
+        <f t="shared" si="0"/>
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="J38" s="2"/>
+    </row>
+    <row r="39" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="25"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="15">
+        <v>1.9</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="74"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="21">
+        <v>5</v>
+      </c>
+      <c r="F40" s="22">
+        <v>8</v>
+      </c>
+      <c r="G40" s="23">
+        <v>14</v>
+      </c>
+      <c r="H40" s="74">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+      <c r="J40" s="2"/>
+    </row>
+    <row r="41" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="21">
         <v>4</v>
       </c>
-      <c r="G12" s="67">
+      <c r="F41" s="22">
         <v>7</v>
       </c>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="65">
-        <v>1</v>
-      </c>
-      <c r="F13" s="66">
-        <v>2</v>
-      </c>
-      <c r="G13" s="67">
-        <v>3</v>
-      </c>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="21" t="s">
+      <c r="G41" s="23">
+        <v>12</v>
+      </c>
+      <c r="H41" s="74">
+        <f t="shared" si="0"/>
+        <v>7.333333333333333</v>
+      </c>
+      <c r="J41" s="2"/>
+    </row>
+    <row r="42" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="25"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="74"/>
+      <c r="J42" s="2"/>
+    </row>
+    <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D43" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="21">
+        <v>6</v>
+      </c>
+      <c r="F43" s="22">
+        <v>10</v>
+      </c>
+      <c r="G43" s="23">
+        <v>16</v>
+      </c>
+      <c r="H43" s="74">
+        <f t="shared" si="0"/>
+        <v>10.333333333333334</v>
+      </c>
+      <c r="J43" s="2"/>
+    </row>
+    <row r="44" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="24"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="21">
+        <v>5</v>
+      </c>
+      <c r="F44" s="22">
+        <v>9</v>
+      </c>
+      <c r="G44" s="23">
+        <v>14</v>
+      </c>
+      <c r="H44" s="74">
+        <f t="shared" si="0"/>
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="J44" s="2"/>
+    </row>
+    <row r="45" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="25"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="74"/>
+      <c r="J45" s="2"/>
+    </row>
+    <row r="46" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E46" s="21">
+        <v>16</v>
+      </c>
+      <c r="F46" s="22">
+        <v>25</v>
+      </c>
+      <c r="G46" s="23">
+        <v>40</v>
+      </c>
+      <c r="H46" s="74">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="J46" s="2"/>
+    </row>
+    <row r="47" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="24"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" s="21">
+        <v>16</v>
+      </c>
+      <c r="F47" s="22">
+        <v>25</v>
+      </c>
+      <c r="G47" s="23">
+        <v>40</v>
+      </c>
+      <c r="H47" s="74">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="J47" s="2"/>
+    </row>
+    <row r="48" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="25"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="74"/>
+      <c r="J48" s="2"/>
+    </row>
+    <row r="49" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="24"/>
+      <c r="B49" s="24"/>
+      <c r="C49" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E49" s="21">
         <v>4</v>
       </c>
-      <c r="E14" s="65">
-        <v>1</v>
-      </c>
-      <c r="F14" s="66">
-        <v>2</v>
-      </c>
-      <c r="G14" s="67">
-        <v>4</v>
-      </c>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="26"/>
-      <c r="C15" s="16">
-        <v>1.2</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="27" t="s">
+      <c r="F49" s="22">
         <v>6</v>
       </c>
-      <c r="E16" s="65">
-        <v>3</v>
-      </c>
-      <c r="F16" s="66">
-        <v>5</v>
-      </c>
-      <c r="G16" s="67">
-        <v>8</v>
-      </c>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="65">
-        <v>1</v>
-      </c>
-      <c r="F17" s="66">
-        <v>2</v>
-      </c>
-      <c r="G17" s="67">
-        <v>4</v>
-      </c>
-      <c r="J17" s="2"/>
-    </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="65">
-        <v>2</v>
-      </c>
-      <c r="F18" s="66">
-        <v>4</v>
-      </c>
-      <c r="G18" s="67">
+      <c r="G49" s="23">
+        <v>10</v>
+      </c>
+      <c r="H49" s="74">
+        <f t="shared" si="0"/>
+        <v>6.333333333333333</v>
+      </c>
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="24"/>
+      <c r="B50" s="24"/>
+      <c r="C50" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="21">
         <v>6</v>
       </c>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="65">
-        <v>2</v>
-      </c>
-      <c r="F19" s="66">
-        <v>4</v>
-      </c>
-      <c r="G19" s="67">
-        <v>6</v>
-      </c>
-      <c r="J19" s="2"/>
-    </row>
-    <row r="20" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="27" t="s">
+      <c r="F50" s="22">
         <v>10</v>
       </c>
-      <c r="E21" s="65">
-        <v>2</v>
-      </c>
-      <c r="F21" s="66">
-        <v>4</v>
-      </c>
-      <c r="G21" s="67">
-        <v>6</v>
-      </c>
-      <c r="J21" s="2"/>
-    </row>
-    <row r="22" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="65">
-        <v>1</v>
-      </c>
-      <c r="F22" s="66">
-        <v>2</v>
-      </c>
-      <c r="G22" s="67">
-        <v>4</v>
-      </c>
-      <c r="J22" s="2"/>
-    </row>
-    <row r="23" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="65">
-        <v>1</v>
-      </c>
-      <c r="F23" s="66">
-        <v>2</v>
-      </c>
-      <c r="G23" s="67">
-        <v>3</v>
-      </c>
-      <c r="J23" s="2"/>
-    </row>
-    <row r="24" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="16">
-        <v>1.4</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="J24" s="2"/>
-    </row>
-    <row r="25" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="E25" s="65">
-        <v>2</v>
-      </c>
-      <c r="F25" s="66">
-        <v>4</v>
-      </c>
-      <c r="G25" s="67">
-        <v>6</v>
-      </c>
-      <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D26" s="27" t="s">
+      <c r="G50" s="23">
         <v>16</v>
       </c>
-      <c r="E26" s="65">
-        <v>3</v>
-      </c>
-      <c r="F26" s="66">
-        <v>5</v>
-      </c>
-      <c r="G26" s="67">
-        <v>8</v>
-      </c>
-      <c r="J26" s="2"/>
-    </row>
-    <row r="27" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="65">
-        <v>2</v>
-      </c>
-      <c r="F27" s="66">
-        <v>4</v>
-      </c>
-      <c r="G27" s="67">
-        <v>6</v>
-      </c>
-      <c r="J27" s="2"/>
-    </row>
-    <row r="28" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="16">
-        <v>1.5</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="J28" s="2"/>
-    </row>
-    <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E29" s="22">
-        <v>3</v>
-      </c>
-      <c r="F29" s="23">
-        <v>5</v>
-      </c>
-      <c r="G29" s="24">
-        <v>7</v>
-      </c>
-      <c r="J29" s="2"/>
-    </row>
-    <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="29"/>
-      <c r="B30" s="29"/>
-      <c r="C30" s="16">
-        <v>1.6</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="J30" s="2"/>
-    </row>
-    <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" s="32">
-        <v>1</v>
-      </c>
-      <c r="F31" s="33">
-        <v>2</v>
-      </c>
-      <c r="G31" s="24">
-        <v>4</v>
-      </c>
-      <c r="J31" s="2"/>
-    </row>
-    <row r="32" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" s="22">
-        <v>1</v>
-      </c>
-      <c r="F32" s="23">
-        <v>2</v>
-      </c>
-      <c r="G32" s="24">
-        <v>4</v>
-      </c>
-      <c r="J32" s="2"/>
-    </row>
-    <row r="33" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="26"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="16">
-        <v>1.7</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="J33" s="2"/>
-    </row>
-    <row r="34" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="25"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E34" s="22">
-        <v>2</v>
-      </c>
-      <c r="F34" s="23">
-        <v>4</v>
-      </c>
-      <c r="G34" s="24">
-        <v>7</v>
-      </c>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="25"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="22">
-        <v>2</v>
-      </c>
-      <c r="F35" s="23">
-        <v>4</v>
-      </c>
-      <c r="G35" s="24">
-        <v>6</v>
-      </c>
-      <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="26"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="16">
-        <v>1.8</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="J36" s="2"/>
-    </row>
-    <row r="37" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37" s="22">
-        <v>1</v>
-      </c>
-      <c r="F37" s="23">
-        <v>2</v>
-      </c>
-      <c r="G37" s="24">
-        <v>4</v>
-      </c>
-      <c r="J37" s="2"/>
-    </row>
-    <row r="38" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="25"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="22">
-        <v>1</v>
-      </c>
-      <c r="F38" s="23">
-        <v>2</v>
-      </c>
-      <c r="G38" s="24">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2"/>
-    </row>
-    <row r="39" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="26"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="16">
-        <v>1.9</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="J39" s="2"/>
-    </row>
-    <row r="40" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="25"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="22">
-        <v>2</v>
-      </c>
-      <c r="F40" s="23">
-        <v>4</v>
-      </c>
-      <c r="G40" s="24">
-        <v>7</v>
-      </c>
-      <c r="J40" s="2"/>
-    </row>
-    <row r="41" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="25"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" s="22">
-        <v>2</v>
-      </c>
-      <c r="F41" s="23">
-        <v>4</v>
-      </c>
-      <c r="G41" s="24">
-        <v>6</v>
-      </c>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="26"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="J42" s="2"/>
-    </row>
-    <row r="43" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="25"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D43" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43" s="22">
-        <v>2</v>
-      </c>
-      <c r="F43" s="23">
-        <v>4</v>
-      </c>
-      <c r="G43" s="24">
-        <v>6</v>
-      </c>
-      <c r="J43" s="2"/>
-    </row>
-    <row r="44" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="25"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="E44" s="22">
-        <v>2</v>
-      </c>
-      <c r="F44" s="23">
-        <v>4</v>
-      </c>
-      <c r="G44" s="24">
-        <v>7</v>
-      </c>
-      <c r="J44" s="2"/>
-    </row>
-    <row r="45" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="26"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="J45" s="2"/>
-    </row>
-    <row r="46" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="25"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D46" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="E46" s="22">
-        <v>5</v>
-      </c>
-      <c r="F46" s="23">
-        <v>8</v>
-      </c>
-      <c r="G46" s="24">
-        <v>14</v>
-      </c>
-      <c r="J46" s="2"/>
-    </row>
-    <row r="47" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="25"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E47" s="22">
-        <v>2</v>
-      </c>
-      <c r="F47" s="23">
-        <v>4</v>
-      </c>
-      <c r="G47" s="24">
-        <v>6</v>
-      </c>
-      <c r="J47" s="2"/>
-    </row>
-    <row r="48" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="26"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="J48" s="2"/>
-    </row>
-    <row r="49" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="25"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D49" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E49" s="22">
-        <v>1</v>
-      </c>
-      <c r="F49" s="23">
-        <v>3</v>
-      </c>
-      <c r="G49" s="24">
-        <v>5</v>
-      </c>
-      <c r="J49" s="2"/>
-    </row>
-    <row r="50" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="25"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="D50" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E50" s="22">
-        <v>2</v>
-      </c>
-      <c r="F50" s="23">
-        <v>4</v>
-      </c>
-      <c r="G50" s="24">
-        <v>7</v>
+      <c r="H50" s="74">
+        <f t="shared" si="0"/>
+        <v>10.333333333333334</v>
       </c>
       <c r="J50" s="2"/>
     </row>
     <row r="51" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="19"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="34"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="38"/>
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="74"/>
       <c r="J51" s="2"/>
     </row>
     <row r="52" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="11"/>
-      <c r="B52" s="39">
+      <c r="B52" s="38">
         <v>2</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="40" t="s">
+      <c r="D52" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="E52" s="41"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="43"/>
+      <c r="E52" s="40"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="74"/>
       <c r="J52" s="2"/>
     </row>
     <row r="53" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="19"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="44">
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="43">
         <v>2.1</v>
       </c>
-      <c r="D53" s="27" t="s">
+      <c r="D53" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E53" s="21">
+        <v>6</v>
+      </c>
+      <c r="F53" s="22">
+        <v>10</v>
+      </c>
+      <c r="G53" s="23">
+        <v>16</v>
+      </c>
+      <c r="H53" s="74">
+        <f t="shared" si="0"/>
+        <v>10.333333333333334</v>
+      </c>
+      <c r="J53" s="2"/>
+    </row>
+    <row r="54" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="43">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D54" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" s="21">
+        <v>5</v>
+      </c>
+      <c r="F54" s="22">
+        <v>8</v>
+      </c>
+      <c r="G54" s="23">
+        <v>14</v>
+      </c>
+      <c r="H54" s="74">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+      <c r="J54" s="2"/>
+    </row>
+    <row r="55" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="43">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D55" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="E53" s="22">
+      <c r="E55" s="21">
         <v>3</v>
       </c>
-      <c r="F53" s="23">
+      <c r="F55" s="22">
         <v>5</v>
       </c>
-      <c r="G53" s="24">
+      <c r="G55" s="23">
+        <v>9</v>
+      </c>
+      <c r="H55" s="74">
+        <f t="shared" si="0"/>
+        <v>5.333333333333333</v>
+      </c>
+      <c r="J55" s="2"/>
+    </row>
+    <row r="56" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="43">
+        <v>2.4</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="E56" s="21">
+        <v>4</v>
+      </c>
+      <c r="F56" s="22">
+        <v>7</v>
+      </c>
+      <c r="G56" s="23">
+        <v>12</v>
+      </c>
+      <c r="H56" s="74">
+        <f t="shared" si="0"/>
+        <v>7.333333333333333</v>
+      </c>
+      <c r="J56" s="2"/>
+    </row>
+    <row r="57" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="43">
+        <v>2.5</v>
+      </c>
+      <c r="D57" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="E57" s="21">
+        <v>3</v>
+      </c>
+      <c r="F57" s="22">
+        <v>5</v>
+      </c>
+      <c r="G57" s="23">
         <v>8</v>
       </c>
-      <c r="J53" s="2"/>
-    </row>
-    <row r="54" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="19"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="44">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D54" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E54" s="22">
-        <v>2</v>
-      </c>
-      <c r="F54" s="23">
-        <v>4</v>
-      </c>
-      <c r="G54" s="24">
-        <v>6</v>
-      </c>
-      <c r="J54" s="2"/>
-    </row>
-    <row r="55" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="19"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="44">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="D55" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="E55" s="22">
-        <v>1</v>
-      </c>
-      <c r="F55" s="23">
-        <v>2</v>
-      </c>
-      <c r="G55" s="24">
-        <v>4</v>
-      </c>
-      <c r="J55" s="2"/>
-    </row>
-    <row r="56" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="19"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="44">
-        <v>2.4</v>
-      </c>
-      <c r="D56" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="E56" s="22">
-        <v>2</v>
-      </c>
-      <c r="F56" s="23">
-        <v>3</v>
-      </c>
-      <c r="G56" s="24">
-        <v>5</v>
-      </c>
-      <c r="J56" s="2"/>
-    </row>
-    <row r="57" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="19"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="44">
-        <v>2.5</v>
-      </c>
-      <c r="D57" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="E57" s="22">
-        <v>1</v>
-      </c>
-      <c r="F57" s="23">
-        <v>2</v>
-      </c>
-      <c r="G57" s="24">
-        <v>3</v>
+      <c r="H57" s="74">
+        <f t="shared" si="0"/>
+        <v>5.166666666666667</v>
       </c>
       <c r="J57" s="2"/>
     </row>
     <row r="58" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="19"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="34"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="38"/>
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="36"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="74"/>
       <c r="J58" s="2"/>
     </row>
     <row r="59" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="11"/>
       <c r="B59" s="11"/>
-      <c r="C59" s="45">
+      <c r="C59" s="44">
         <v>3</v>
       </c>
-      <c r="D59" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="E59" s="41"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="43"/>
+      <c r="D59" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="E59" s="40"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="42"/>
+      <c r="H59" s="74"/>
       <c r="J59" s="2"/>
     </row>
     <row r="60" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="19"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="44">
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="43">
         <v>3.1</v>
       </c>
-      <c r="D60" s="27" t="s">
+      <c r="D60" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E60" s="21">
+        <v>5</v>
+      </c>
+      <c r="F60" s="22">
+        <v>8</v>
+      </c>
+      <c r="G60" s="23">
+        <v>12</v>
+      </c>
+      <c r="H60" s="74">
+        <f t="shared" si="0"/>
+        <v>8.1666666666666661</v>
+      </c>
+      <c r="J60" s="2"/>
+    </row>
+    <row r="61" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="43">
+        <v>3.2</v>
+      </c>
+      <c r="D61" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="E60" s="22">
-        <v>2</v>
-      </c>
-      <c r="F60" s="23">
+      <c r="E61" s="21">
+        <v>3</v>
+      </c>
+      <c r="F61" s="22">
+        <v>5</v>
+      </c>
+      <c r="G61" s="23">
+        <v>8</v>
+      </c>
+      <c r="H61" s="74">
+        <f t="shared" si="0"/>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="J61" s="2"/>
+    </row>
+    <row r="62" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="43">
+        <v>3.3</v>
+      </c>
+      <c r="D62" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="E62" s="21">
+        <v>6</v>
+      </c>
+      <c r="F62" s="22">
+        <v>9</v>
+      </c>
+      <c r="G62" s="23">
+        <v>14</v>
+      </c>
+      <c r="H62" s="74">
+        <f t="shared" si="0"/>
+        <v>9.3333333333333339</v>
+      </c>
+      <c r="J62" s="2"/>
+    </row>
+    <row r="63" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="43">
+        <v>3.4</v>
+      </c>
+      <c r="D63" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E63" s="21">
         <v>4</v>
       </c>
-      <c r="G60" s="24">
+      <c r="F63" s="22">
         <v>6</v>
       </c>
-      <c r="J60" s="2"/>
-    </row>
-    <row r="61" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="19"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="44">
-        <v>3.2</v>
-      </c>
-      <c r="D61" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E61" s="22">
-        <v>1</v>
-      </c>
-      <c r="F61" s="23">
-        <v>2</v>
-      </c>
-      <c r="G61" s="24">
-        <v>4</v>
-      </c>
-      <c r="J61" s="2"/>
-    </row>
-    <row r="62" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="19"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="44">
-        <v>3.3</v>
-      </c>
-      <c r="D62" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="E62" s="22">
-        <v>2</v>
-      </c>
-      <c r="F62" s="23">
-        <v>3</v>
-      </c>
-      <c r="G62" s="24">
-        <v>5</v>
-      </c>
-      <c r="J62" s="2"/>
-    </row>
-    <row r="63" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="19"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="44">
-        <v>3.4</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="E63" s="22">
-        <v>1</v>
-      </c>
-      <c r="F63" s="23">
-        <v>2</v>
-      </c>
-      <c r="G63" s="24">
-        <v>4</v>
+      <c r="G63" s="23">
+        <v>10</v>
+      </c>
+      <c r="H63" s="74">
+        <f t="shared" si="0"/>
+        <v>6.333333333333333</v>
       </c>
       <c r="J63" s="2"/>
     </row>
     <row r="64" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="19"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="34"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="38"/>
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="37"/>
+      <c r="H64" s="74"/>
       <c r="J64" s="2"/>
     </row>
     <row r="65" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="11"/>
       <c r="B65" s="11"/>
-      <c r="C65" s="45">
+      <c r="C65" s="44">
         <v>4</v>
       </c>
-      <c r="D65" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="E65" s="46"/>
-      <c r="F65" s="47"/>
-      <c r="G65" s="48"/>
+      <c r="D65" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="E65" s="45"/>
+      <c r="F65" s="46"/>
+      <c r="G65" s="47"/>
+      <c r="H65" s="74"/>
       <c r="J65" s="2"/>
     </row>
     <row r="66" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="19"/>
-      <c r="B66" s="19"/>
-      <c r="C66" s="44">
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="43">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D66" s="27" t="s">
+      <c r="D66" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="E66" s="22">
-        <v>1</v>
-      </c>
-      <c r="F66" s="23">
+      <c r="E66" s="21">
+        <v>4</v>
+      </c>
+      <c r="F66" s="22">
+        <v>6</v>
+      </c>
+      <c r="G66" s="48">
+        <v>9</v>
+      </c>
+      <c r="H66" s="74">
+        <f t="shared" si="0"/>
+        <v>6.166666666666667</v>
+      </c>
+      <c r="J66" s="2"/>
+    </row>
+    <row r="67" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="43">
+        <v>4.2</v>
+      </c>
+      <c r="D67" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="E67" s="21">
+        <v>3</v>
+      </c>
+      <c r="F67" s="22">
+        <v>5</v>
+      </c>
+      <c r="G67" s="48">
+        <v>8</v>
+      </c>
+      <c r="H67" s="74">
+        <f t="shared" si="0"/>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="J67" s="2"/>
+    </row>
+    <row r="68" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="43">
+        <v>4.3</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="E68" s="21">
         <v>2</v>
       </c>
-      <c r="G66" s="49">
+      <c r="F68" s="22">
         <v>3</v>
       </c>
-      <c r="J66" s="2"/>
-    </row>
-    <row r="67" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="19"/>
-      <c r="B67" s="19"/>
-      <c r="C67" s="44">
-        <v>4.2</v>
-      </c>
-      <c r="D67" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="E67" s="22">
-        <v>1</v>
-      </c>
-      <c r="F67" s="23">
-        <v>2</v>
-      </c>
-      <c r="G67" s="49">
-        <v>3</v>
-      </c>
-      <c r="J67" s="2"/>
-    </row>
-    <row r="68" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="19"/>
-      <c r="B68" s="19"/>
-      <c r="C68" s="44">
-        <v>4.3</v>
-      </c>
-      <c r="D68" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="E68" s="22">
-        <v>1</v>
-      </c>
-      <c r="F68" s="23">
-        <v>2</v>
-      </c>
-      <c r="G68" s="49">
-        <v>3</v>
+      <c r="G68" s="48">
+        <v>5</v>
+      </c>
+      <c r="H68" s="74">
+        <f t="shared" si="0"/>
+        <v>3.1666666666666665</v>
       </c>
       <c r="J68" s="2"/>
     </row>
     <row r="69" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="19"/>
-      <c r="B69" s="50"/>
-      <c r="C69" s="51"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="38"/>
+      <c r="A69" s="18"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="50"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="35"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="37"/>
+      <c r="H69" s="74"/>
       <c r="J69" s="2"/>
     </row>
     <row r="70" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="11"/>
       <c r="B70" s="11"/>
-      <c r="C70" s="45">
+      <c r="C70" s="44">
         <v>5</v>
       </c>
-      <c r="D70" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="E70" s="41"/>
-      <c r="F70" s="42"/>
-      <c r="G70" s="43"/>
+      <c r="D70" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="E70" s="40"/>
+      <c r="F70" s="41"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="74"/>
       <c r="J70" s="2"/>
     </row>
     <row r="71" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="19"/>
-      <c r="B71" s="19"/>
-      <c r="C71" s="44">
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="43">
         <v>5.0999999999999996</v>
       </c>
-      <c r="D71" s="27" t="s">
+      <c r="D71" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="E71" s="22">
-        <v>1</v>
-      </c>
-      <c r="F71" s="23">
+      <c r="E71" s="21">
+        <v>3</v>
+      </c>
+      <c r="F71" s="22">
+        <v>5</v>
+      </c>
+      <c r="G71" s="23">
+        <v>8</v>
+      </c>
+      <c r="H71" s="74">
+        <f t="shared" si="0"/>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="J71" s="2"/>
+    </row>
+    <row r="72" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="43">
+        <v>5.2</v>
+      </c>
+      <c r="D72" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E72" s="21">
+        <v>4</v>
+      </c>
+      <c r="F72" s="22">
+        <v>6</v>
+      </c>
+      <c r="G72" s="23">
+        <v>10</v>
+      </c>
+      <c r="H72" s="74">
+        <f t="shared" si="0"/>
+        <v>6.333333333333333</v>
+      </c>
+      <c r="J72" s="2"/>
+    </row>
+    <row r="73" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="51">
+        <v>5.3</v>
+      </c>
+      <c r="D73" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E73" s="31">
+        <v>6</v>
+      </c>
+      <c r="F73" s="32">
+        <v>10</v>
+      </c>
+      <c r="G73" s="52">
+        <v>16</v>
+      </c>
+      <c r="H73" s="74">
+        <f t="shared" si="0"/>
+        <v>10.333333333333334</v>
+      </c>
+      <c r="J73" s="2"/>
+    </row>
+    <row r="74" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="43">
+        <v>5.4</v>
+      </c>
+      <c r="D74" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="E74" s="21">
         <v>2</v>
       </c>
-      <c r="G71" s="24">
+      <c r="F74" s="22">
         <v>3</v>
       </c>
-      <c r="J71" s="2"/>
-    </row>
-    <row r="72" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="19"/>
-      <c r="B72" s="19"/>
-      <c r="C72" s="44">
-        <v>5.2</v>
-      </c>
-      <c r="D72" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="E72" s="22">
-        <v>1</v>
-      </c>
-      <c r="F72" s="23">
-        <v>2</v>
-      </c>
-      <c r="G72" s="24">
-        <v>3</v>
-      </c>
-      <c r="J72" s="2"/>
-    </row>
-    <row r="73" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="19"/>
-      <c r="B73" s="19"/>
-      <c r="C73" s="52">
-        <v>5.3</v>
-      </c>
-      <c r="D73" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="E73" s="32">
-        <v>2</v>
-      </c>
-      <c r="F73" s="33">
-        <v>3</v>
-      </c>
-      <c r="G73" s="53">
+      <c r="G74" s="23">
         <v>5</v>
       </c>
-      <c r="J73" s="2"/>
-    </row>
-    <row r="74" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="19"/>
-      <c r="B74" s="19"/>
-      <c r="C74" s="44">
-        <v>5.4</v>
-      </c>
-      <c r="D74" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="E74" s="22">
-        <v>1</v>
-      </c>
-      <c r="F74" s="23">
-        <v>2</v>
-      </c>
-      <c r="G74" s="24">
-        <v>3</v>
+      <c r="H74" s="74">
+        <f t="shared" si="0"/>
+        <v>3.1666666666666665</v>
       </c>
       <c r="J74" s="2"/>
     </row>
     <row r="75" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="19"/>
-      <c r="B75" s="50"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="28"/>
-      <c r="E75" s="36"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="38"/>
+      <c r="A75" s="18"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="50"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="35"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="37"/>
+      <c r="H75" s="74"/>
       <c r="J75" s="2"/>
     </row>
     <row r="76" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="11"/>
-      <c r="B76" s="54"/>
-      <c r="C76" s="55">
+      <c r="B76" s="53"/>
+      <c r="C76" s="54">
         <v>6</v>
       </c>
-      <c r="D76" s="56" t="s">
+      <c r="D76" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="E76" s="40"/>
+      <c r="F76" s="41"/>
+      <c r="G76" s="42"/>
+      <c r="H76" s="74"/>
+      <c r="J76" s="2"/>
+    </row>
+    <row r="77" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="43">
+        <v>6.1</v>
+      </c>
+      <c r="D77" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="E77" s="21">
+        <v>2</v>
+      </c>
+      <c r="F77" s="22">
+        <v>3</v>
+      </c>
+      <c r="G77" s="23">
+        <v>5</v>
+      </c>
+      <c r="H77" s="74">
+        <f t="shared" ref="H76:H87" si="1">(E77 + 4*F77 + G77)/6</f>
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="J77" s="2"/>
+    </row>
+    <row r="78" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="43">
+        <v>6.2</v>
+      </c>
+      <c r="D78" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E78" s="21">
+        <v>12</v>
+      </c>
+      <c r="F78" s="22">
+        <v>20</v>
+      </c>
+      <c r="G78" s="23">
+        <v>30</v>
+      </c>
+      <c r="H78" s="74">
+        <f t="shared" si="1"/>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="J78" s="2"/>
+    </row>
+    <row r="79" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="43">
+        <v>6.3</v>
+      </c>
+      <c r="D79" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="E79" s="21">
+        <v>3</v>
+      </c>
+      <c r="F79" s="22">
+        <v>5</v>
+      </c>
+      <c r="G79" s="23">
+        <v>8</v>
+      </c>
+      <c r="H79" s="74">
+        <f t="shared" si="1"/>
+        <v>5.166666666666667</v>
+      </c>
+      <c r="J79" s="2"/>
+    </row>
+    <row r="80" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="43">
+        <v>6.4</v>
+      </c>
+      <c r="D80" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E80" s="21">
+        <v>3</v>
+      </c>
+      <c r="F80" s="22">
+        <v>4</v>
+      </c>
+      <c r="G80" s="23">
+        <v>7</v>
+      </c>
+      <c r="H80" s="74">
+        <f t="shared" si="1"/>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="J80" s="2"/>
+    </row>
+    <row r="81" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="43">
+        <v>6.5</v>
+      </c>
+      <c r="D81" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="E81" s="21">
+        <v>6</v>
+      </c>
+      <c r="F81" s="22">
+        <v>10</v>
+      </c>
+      <c r="G81" s="23">
+        <v>15</v>
+      </c>
+      <c r="H81" s="74">
+        <f t="shared" si="1"/>
+        <v>10.166666666666666</v>
+      </c>
+      <c r="J81" s="2"/>
+    </row>
+    <row r="82" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="49"/>
+      <c r="B82" s="49"/>
+      <c r="C82" s="50"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="35"/>
+      <c r="F82" s="36"/>
+      <c r="G82" s="37"/>
+      <c r="H82" s="74"/>
+      <c r="J82" s="2"/>
+    </row>
+    <row r="83" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="56"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="54">
+        <v>7</v>
+      </c>
+      <c r="D83" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="E76" s="41"/>
-      <c r="F76" s="42"/>
-      <c r="G76" s="43"/>
-      <c r="J76" s="2"/>
-    </row>
-    <row r="77" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="19"/>
-      <c r="B77" s="19"/>
-      <c r="C77" s="44">
-        <v>6.1</v>
-      </c>
-      <c r="D77" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="E77" s="22">
-        <v>1</v>
-      </c>
-      <c r="F77" s="23">
-        <v>2</v>
-      </c>
-      <c r="G77" s="24">
-        <v>3</v>
-      </c>
-      <c r="J77" s="2"/>
-    </row>
-    <row r="78" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="19"/>
-      <c r="B78" s="19"/>
-      <c r="C78" s="44">
-        <v>6.2</v>
-      </c>
-      <c r="D78" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="E78" s="22">
-        <v>5</v>
-      </c>
-      <c r="F78" s="23">
+      <c r="E83" s="40"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="42"/>
+      <c r="H83" s="74"/>
+      <c r="J83" s="2"/>
+    </row>
+    <row r="84" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="18"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="43">
+        <v>7.1</v>
+      </c>
+      <c r="D84" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E84" s="21">
+        <v>6</v>
+      </c>
+      <c r="F84" s="22">
+        <v>12</v>
+      </c>
+      <c r="G84" s="23">
+        <v>20</v>
+      </c>
+      <c r="H84" s="74">
+        <f t="shared" si="1"/>
+        <v>12.333333333333334</v>
+      </c>
+      <c r="J84" s="2"/>
+    </row>
+    <row r="85" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="24"/>
+      <c r="B85" s="24"/>
+      <c r="C85" s="43">
+        <v>7.2</v>
+      </c>
+      <c r="D85" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="E85" s="21">
         <v>8</v>
       </c>
-      <c r="G78" s="24">
+      <c r="F85" s="22">
         <v>12</v>
       </c>
-      <c r="J78" s="2"/>
-    </row>
-    <row r="79" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="19"/>
-      <c r="B79" s="19"/>
-      <c r="C79" s="44">
-        <v>6.3</v>
-      </c>
-      <c r="D79" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="E79" s="22">
-        <v>1</v>
-      </c>
-      <c r="F79" s="23">
-        <v>2</v>
-      </c>
-      <c r="G79" s="24">
-        <v>4</v>
-      </c>
-      <c r="J79" s="2"/>
-    </row>
-    <row r="80" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="19"/>
-      <c r="B80" s="19"/>
-      <c r="C80" s="44">
-        <v>6.4</v>
-      </c>
-      <c r="D80" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="E80" s="22">
-        <v>1</v>
-      </c>
-      <c r="F80" s="23">
-        <v>2</v>
-      </c>
-      <c r="G80" s="24">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2"/>
-    </row>
-    <row r="81" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="19"/>
-      <c r="B81" s="19"/>
-      <c r="C81" s="44">
-        <v>6.5</v>
-      </c>
-      <c r="D81" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="E81" s="22">
-        <v>2</v>
-      </c>
-      <c r="F81" s="23">
-        <v>4</v>
-      </c>
-      <c r="G81" s="24">
+      <c r="G85" s="23">
+        <v>18</v>
+      </c>
+      <c r="H85" s="74">
+        <f t="shared" si="1"/>
+        <v>12.333333333333334</v>
+      </c>
+      <c r="J85" s="2"/>
+    </row>
+    <row r="86" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="18"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="43">
+        <v>7.3</v>
+      </c>
+      <c r="D86" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E86" s="21">
+        <v>10</v>
+      </c>
+      <c r="F86" s="22">
+        <v>16</v>
+      </c>
+      <c r="G86" s="23">
+        <v>24</v>
+      </c>
+      <c r="H86" s="74">
+        <f t="shared" si="1"/>
+        <v>16.333333333333332</v>
+      </c>
+      <c r="J86" s="2"/>
+    </row>
+    <row r="87" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="18"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="43">
+        <v>7.4</v>
+      </c>
+      <c r="D87" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="E87" s="21">
         <v>6</v>
       </c>
-      <c r="J81" s="2"/>
-    </row>
-    <row r="82" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="50"/>
-      <c r="B82" s="50"/>
-      <c r="C82" s="51"/>
-      <c r="D82" s="28"/>
-      <c r="E82" s="36"/>
-      <c r="F82" s="37"/>
-      <c r="G82" s="38"/>
-      <c r="J82" s="2"/>
-    </row>
-    <row r="83" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="57"/>
-      <c r="B83" s="58"/>
-      <c r="C83" s="55">
-        <v>7</v>
-      </c>
-      <c r="D83" s="56" t="s">
+      <c r="F87" s="22">
+        <v>10</v>
+      </c>
+      <c r="G87" s="23">
+        <v>16</v>
+      </c>
+      <c r="H87" s="74">
+        <f t="shared" si="1"/>
+        <v>10.333333333333334</v>
+      </c>
+      <c r="J87" s="2"/>
+    </row>
+    <row r="88" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="18"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="50"/>
+      <c r="D88" s="27"/>
+      <c r="E88" s="35"/>
+      <c r="F88" s="36"/>
+      <c r="G88" s="37"/>
+      <c r="J88" s="2"/>
+    </row>
+    <row r="89" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="58" t="s">
         <v>95</v>
       </c>
-      <c r="E83" s="41"/>
-      <c r="F83" s="42"/>
-      <c r="G83" s="43"/>
-      <c r="J83" s="2"/>
-    </row>
-    <row r="84" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="19"/>
-      <c r="B84" s="19"/>
-      <c r="C84" s="44">
-        <v>7.1</v>
-      </c>
-      <c r="D84" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="E84" s="22">
-        <v>8</v>
-      </c>
-      <c r="F84" s="23">
-        <v>16</v>
-      </c>
-      <c r="G84" s="24">
-        <v>24</v>
-      </c>
-      <c r="J84" s="2"/>
-    </row>
-    <row r="85" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="25"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="44">
-        <v>7.2</v>
-      </c>
-      <c r="D85" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="E85" s="22">
-        <v>8</v>
-      </c>
-      <c r="F85" s="23">
-        <v>16</v>
-      </c>
-      <c r="G85" s="24">
-        <v>24</v>
-      </c>
-      <c r="J85" s="2"/>
-    </row>
-    <row r="86" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="19"/>
-      <c r="B86" s="19"/>
-      <c r="C86" s="44">
-        <v>7.3</v>
-      </c>
-      <c r="D86" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="E86" s="22">
-        <v>8</v>
-      </c>
-      <c r="F86" s="23">
-        <v>16</v>
-      </c>
-      <c r="G86" s="24">
-        <v>24</v>
-      </c>
-      <c r="J86" s="2"/>
-    </row>
-    <row r="87" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="19"/>
-      <c r="B87" s="19"/>
-      <c r="C87" s="44">
-        <v>7.4</v>
-      </c>
-      <c r="D87" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="E87" s="22">
-        <v>8</v>
-      </c>
-      <c r="F87" s="23">
-        <v>16</v>
-      </c>
-      <c r="G87" s="24">
-        <v>24</v>
-      </c>
-      <c r="J87" s="2"/>
-    </row>
-    <row r="88" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="19"/>
-      <c r="B88" s="19"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="28"/>
-      <c r="E88" s="36"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="38"/>
-      <c r="H88" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="J88" s="2"/>
-    </row>
-    <row r="89" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="59" t="s">
-        <v>96</v>
-      </c>
-      <c r="B89" s="19"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="37"/>
-      <c r="E89" s="60">
+      <c r="B89" s="18"/>
+      <c r="C89" s="50"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="59">
         <f>SUM(E10:E87)</f>
-        <v>120</v>
-      </c>
-      <c r="F89" s="60">
-        <f t="shared" ref="F89:G89" si="0">SUM(F10:F87)</f>
-        <v>230</v>
-      </c>
-      <c r="G89" s="60">
-        <f t="shared" si="0"/>
-        <v>366</v>
-      </c>
-      <c r="H89" s="60">
-        <f>SUM(E89:G89)</f>
-        <v>716</v>
+        <v>293</v>
+      </c>
+      <c r="F89" s="59">
+        <f t="shared" ref="F89:H89" si="2">SUM(F10:F87)</f>
+        <v>474</v>
+      </c>
+      <c r="G89" s="59">
+        <f t="shared" si="2"/>
+        <v>751</v>
+      </c>
+      <c r="H89" s="59">
+        <f>SUM(H10:H87)</f>
+        <v>489.99999999999994</v>
       </c>
       <c r="J89" s="2"/>
     </row>
